--- a/xlsx/Power/pgroups1.xlsx
+++ b/xlsx/Power/pgroups1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABE1352-F4AF-4470-B8F6-043960BEA8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AB60F2-7AE1-40CB-9685-47F091A86318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{D11AA3D4-DF61-4AE1-B61C-7BC3DF640D69}"/>
+    <workbookView xWindow="4485" yWindow="3945" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{D11AA3D4-DF61-4AE1-B61C-7BC3DF640D69}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.38600000000000001</v>
       </c>
       <c r="C1">
-        <v>0.27900000000000003</v>
+        <v>0.49199999999999999</v>
       </c>
       <c r="D1">
-        <v>0.39200000000000002</v>
+        <v>0.54900000000000004</v>
       </c>
       <c r="E1">
-        <v>0.45800000000000002</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="F1">
-        <v>0.52700000000000002</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="G1">
-        <v>0.55700000000000005</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="H1">
-        <v>0.6</v>
+        <v>0.67800000000000005</v>
       </c>
       <c r="I1">
-        <v>0.61699999999999999</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="J1">
-        <v>0.66900000000000004</v>
+        <v>0.73399999999999999</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.42699999999999999</v>
       </c>
       <c r="C2">
-        <v>0.30299999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="D2">
-        <v>0.432</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="E2">
-        <v>0.48699999999999999</v>
+        <v>0.63300000000000001</v>
       </c>
       <c r="F2">
-        <v>0.57299999999999995</v>
+        <v>0.68300000000000005</v>
       </c>
       <c r="G2">
-        <v>0.61199999999999999</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="H2">
-        <v>0.63900000000000001</v>
+        <v>0.72599999999999998</v>
       </c>
       <c r="I2">
-        <v>0.66700000000000004</v>
+        <v>0.74</v>
       </c>
       <c r="J2">
-        <v>0.71199999999999997</v>
+        <v>0.76100000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.38200000000000001</v>
       </c>
       <c r="C3">
-        <v>0.504</v>
+        <v>0.47099999999999997</v>
       </c>
       <c r="D3">
-        <v>0.54100000000000004</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="E3">
-        <v>0.57999999999999996</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="F3">
-        <v>0.621</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="G3">
         <v>0.63600000000000001</v>
       </c>
       <c r="H3">
-        <v>0.66500000000000004</v>
+        <v>0.66400000000000003</v>
       </c>
       <c r="I3">
         <v>0.68899999999999995</v>
       </c>
       <c r="J3">
-        <v>0.72799999999999998</v>
+        <v>0.72599999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.29399999999999998</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="B4">
-        <v>0.38400000000000001</v>
+        <v>0.375</v>
       </c>
       <c r="C4">
-        <v>0.46899999999999997</v>
+        <v>0.46700000000000003</v>
       </c>
       <c r="D4">
-        <v>0.52</v>
+        <v>0.52200000000000002</v>
       </c>
       <c r="E4">
         <v>0.56100000000000005</v>
       </c>
       <c r="F4">
-        <v>0.59799999999999998</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="G4">
         <v>0.625</v>
       </c>
       <c r="H4">
-        <v>0.64400000000000002</v>
+        <v>0.64600000000000002</v>
       </c>
       <c r="I4">
-        <v>0.66900000000000004</v>
+        <v>0.67</v>
       </c>
       <c r="J4">
-        <v>0.70899999999999996</v>
+        <v>0.70699999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>0.125</v>
       </c>
       <c r="C5">
-        <v>1E-3</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="D5">
-        <v>1.4999999999999999E-2</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="E5">
-        <v>6.6000000000000003E-2</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="F5">
-        <v>0.11700000000000001</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="G5">
-        <v>0.19900000000000001</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="H5">
-        <v>0.27</v>
+        <v>0.45</v>
       </c>
       <c r="I5">
-        <v>0.35399999999999998</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="J5">
-        <v>0.39600000000000002</v>
+        <v>0.54300000000000004</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.43</v>
       </c>
       <c r="C6">
-        <v>0.627</v>
+        <v>0.52</v>
       </c>
       <c r="D6">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="E6">
         <v>0.626</v>
       </c>
-      <c r="E6">
-        <v>0.65100000000000002</v>
-      </c>
       <c r="F6">
-        <v>0.68700000000000006</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="G6">
-        <v>0.71399999999999997</v>
+        <v>0.71</v>
       </c>
       <c r="H6">
-        <v>0.71899999999999997</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="I6">
-        <v>0.73499999999999999</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="J6">
-        <v>0.77</v>
+        <v>0.76200000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.41499999999999998</v>
       </c>
       <c r="C7">
-        <v>0.48199999999999998</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="D7">
         <v>0.56200000000000006</v>
       </c>
       <c r="E7">
-        <v>0.58599999999999997</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="F7">
-        <v>0.63500000000000001</v>
+        <v>0.63700000000000001</v>
       </c>
       <c r="G7">
-        <v>0.66800000000000004</v>
+        <v>0.67</v>
       </c>
       <c r="H7">
         <v>0.66800000000000004</v>
       </c>
       <c r="I7">
-        <v>0.67600000000000005</v>
+        <v>0.67800000000000005</v>
       </c>
       <c r="J7">
-        <v>0.73</v>
+        <v>0.73199999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="C8">
-        <v>0.14399999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="D8">
-        <v>0.27700000000000002</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="E8">
-        <v>0.32900000000000001</v>
+        <v>0.42899999999999999</v>
       </c>
       <c r="F8">
-        <v>0.378</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="G8">
-        <v>0.40799999999999997</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="H8">
-        <v>0.433</v>
+        <v>0.504</v>
       </c>
       <c r="I8">
-        <v>0.34899999999999998</v>
+        <v>0.54700000000000004</v>
       </c>
       <c r="J8">
-        <v>0.38200000000000001</v>
+        <v>0.57399999999999995</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.23899999999999999</v>
       </c>
       <c r="C9">
-        <v>0.68500000000000005</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="D9">
-        <v>0.91300000000000003</v>
+        <v>0.38800000000000001</v>
       </c>
       <c r="E9">
-        <v>0.73899999999999999</v>
+        <v>0.377</v>
       </c>
       <c r="F9">
-        <v>0.47899999999999998</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="G9">
-        <v>0.438</v>
+        <v>0.4</v>
       </c>
       <c r="H9">
-        <v>0.433</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="I9">
-        <v>0.45</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="J9">
-        <v>0.46600000000000003</v>
+        <v>0.44600000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/pgroups1.xlsx
+++ b/xlsx/Power/pgroups1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AB60F2-7AE1-40CB-9685-47F091A86318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4457733-542B-43D4-841C-FB5D92CE8C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4485" yWindow="3945" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{D11AA3D4-DF61-4AE1-B61C-7BC3DF640D69}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{D11AA3D4-DF61-4AE1-B61C-7BC3DF640D69}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,19 +398,19 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.26100000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="B1">
-        <v>0.38600000000000001</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="C1">
         <v>0.49199999999999999</v>
       </c>
       <c r="D1">
-        <v>0.54900000000000004</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="E1">
-        <v>0.57899999999999996</v>
+        <v>0.58099999999999996</v>
       </c>
       <c r="F1">
         <v>0.64400000000000002</v>
@@ -422,15 +422,15 @@
         <v>0.67800000000000005</v>
       </c>
       <c r="I1">
-        <v>0.70399999999999996</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="J1">
-        <v>0.73399999999999999</v>
+        <v>0.73499999999999999</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.28699999999999998</v>
+        <v>0.28599999999999998</v>
       </c>
       <c r="B2">
         <v>0.42699999999999999</v>
@@ -445,51 +445,51 @@
         <v>0.63300000000000001</v>
       </c>
       <c r="F2">
-        <v>0.68300000000000005</v>
+        <v>0.68200000000000005</v>
       </c>
       <c r="G2">
-        <v>0.70499999999999996</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="H2">
-        <v>0.72599999999999998</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="I2">
-        <v>0.74</v>
+        <v>0.74299999999999999</v>
       </c>
       <c r="J2">
-        <v>0.76100000000000001</v>
+        <v>0.76300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.27200000000000002</v>
+        <v>0.27</v>
       </c>
       <c r="B3">
-        <v>0.38200000000000001</v>
+        <v>0.38400000000000001</v>
       </c>
       <c r="C3">
-        <v>0.47099999999999997</v>
+        <v>0.47199999999999998</v>
       </c>
       <c r="D3">
         <v>0.53500000000000003</v>
       </c>
       <c r="E3">
-        <v>0.57299999999999995</v>
+        <v>0.57799999999999996</v>
       </c>
       <c r="F3">
-        <v>0.61599999999999999</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="G3">
         <v>0.63600000000000001</v>
       </c>
       <c r="H3">
-        <v>0.66400000000000003</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="I3">
-        <v>0.68899999999999995</v>
+        <v>0.69499999999999995</v>
       </c>
       <c r="J3">
-        <v>0.72599999999999998</v>
+        <v>0.73299999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -497,68 +497,68 @@
         <v>0.27400000000000002</v>
       </c>
       <c r="B4">
-        <v>0.375</v>
+        <v>0.379</v>
       </c>
       <c r="C4">
-        <v>0.46700000000000003</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="D4">
-        <v>0.52200000000000002</v>
+        <v>0.52300000000000002</v>
       </c>
       <c r="E4">
-        <v>0.56100000000000005</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="F4">
-        <v>0.59299999999999997</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="G4">
         <v>0.625</v>
       </c>
       <c r="H4">
-        <v>0.64600000000000002</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="I4">
-        <v>0.67</v>
+        <v>0.67700000000000005</v>
       </c>
       <c r="J4">
-        <v>0.70699999999999996</v>
+        <v>0.71599999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.106</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="B5">
-        <v>0.125</v>
+        <v>0.124</v>
       </c>
       <c r="C5">
-        <v>0.18099999999999999</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="D5">
-        <v>0.23499999999999999</v>
+        <v>0.252</v>
       </c>
       <c r="E5">
-        <v>0.28899999999999998</v>
+        <v>0.26200000000000001</v>
       </c>
       <c r="F5">
-        <v>0.33300000000000002</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="G5">
-        <v>0.39700000000000002</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="H5">
-        <v>0.45</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="I5">
-        <v>0.52100000000000002</v>
+        <v>0.314</v>
       </c>
       <c r="J5">
-        <v>0.54300000000000004</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.27800000000000002</v>
+        <v>0.27600000000000002</v>
       </c>
       <c r="B6">
         <v>0.43</v>
@@ -567,39 +567,39 @@
         <v>0.52</v>
       </c>
       <c r="D6">
-        <v>0.59399999999999997</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="E6">
-        <v>0.626</v>
+        <v>0.623</v>
       </c>
       <c r="F6">
-        <v>0.67700000000000005</v>
+        <v>0.67600000000000005</v>
       </c>
       <c r="G6">
-        <v>0.71</v>
+        <v>0.70799999999999996</v>
       </c>
       <c r="H6">
-        <v>0.71599999999999997</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="I6">
         <v>0.73399999999999999</v>
       </c>
       <c r="J6">
-        <v>0.76200000000000001</v>
+        <v>0.76500000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.27600000000000002</v>
+        <v>0.27200000000000002</v>
       </c>
       <c r="B7">
-        <v>0.41499999999999998</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="C7">
-        <v>0.48599999999999999</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="D7">
-        <v>0.56200000000000006</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="E7">
         <v>0.58499999999999996</v>
@@ -608,13 +608,13 @@
         <v>0.63700000000000001</v>
       </c>
       <c r="G7">
-        <v>0.67</v>
+        <v>0.66900000000000004</v>
       </c>
       <c r="H7">
         <v>0.66800000000000004</v>
       </c>
       <c r="I7">
-        <v>0.67800000000000005</v>
+        <v>0.67600000000000005</v>
       </c>
       <c r="J7">
         <v>0.73199999999999998</v>
@@ -631,13 +631,13 @@
         <v>0.35</v>
       </c>
       <c r="D8">
-        <v>0.40400000000000003</v>
+        <v>0.40699999999999997</v>
       </c>
       <c r="E8">
-        <v>0.42899999999999999</v>
+        <v>0.43099999999999999</v>
       </c>
       <c r="F8">
-        <v>0.46500000000000002</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="G8">
         <v>0.48499999999999999</v>
@@ -654,34 +654,34 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>0.216</v>
+        <v>0.217</v>
       </c>
       <c r="B9">
-        <v>0.23899999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="C9">
-        <v>0.47799999999999998</v>
+        <v>0.48</v>
       </c>
       <c r="D9">
-        <v>0.38800000000000001</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="E9">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="F9">
-        <v>0.38900000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="G9">
-        <v>0.4</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="H9">
         <v>0.40899999999999997</v>
       </c>
       <c r="I9">
-        <v>0.42499999999999999</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="J9">
-        <v>0.44600000000000001</v>
+        <v>0.45100000000000001</v>
       </c>
     </row>
   </sheetData>
